--- a/construction_template/data/templates_blank/notification_slip.xlsx
+++ b/construction_template/data/templates_blank/notification_slip.xlsx
@@ -5,7 +5,6 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EmsSuperAllSrc\EmsSupervision\xlt\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86C0028-2E3F-4465-876B-4CE495123F9C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -27,28 +26,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
-    <t>臺北市政府工務局水利工程處</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>預約式工程施工回報單</t>
   </si>
   <si>
-    <t>工程名稱：111年度西區水利建造物檢修改善及災後淤土、樹木復原及設施搶修預約維護工程</t>
+    <t xml:space="preserve">工程名稱：</t>
   </si>
   <si>
     <t>第1次通報單</t>
   </si>
   <si>
-    <t>契約編號：H-111-03-111040</t>
-  </si>
-  <si>
-    <t>通報單編製人員：陳泓光</t>
+    <t xml:space="preserve">契約編號：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通報單編製人員：</t>
   </si>
   <si>
     <t>工程地點</t>
   </si>
   <si>
-    <t>雙溪</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>實際開工日期</t>
@@ -93,14 +92,14 @@
     <t>完工概述:</t>
   </si>
   <si>
-    <t xml:space="preserve">1雙溪雙溪橋至復興橋段堤壁、堤坡、低水護岸及伸縮縫修復。
+    <t xml:space="preserve">
 2.本次通報單係111年度水利建造物檢查缺失項目修復。
 3.每項缺失改善請於回報時，均檢附有時間之施工前、中、後照片。
 4.施工期間承商應依契約勞工安全衛生等相規定辦理，並加強安全措施以維施工安全。
 5.本案1、162、233及279不得辦理追加。</t>
   </si>
   <si>
-    <t>1雙溪雙溪橋至復興橋段堤壁、堤坡、低水護岸及伸縮縫修復。</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">監造單位            工務科          設計單位            總工程司室　　</t>

--- a/construction_template/data/templates_blank/notification_slip.xlsx
+++ b/construction_template/data/templates_blank/notification_slip.xlsx
@@ -5,6 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86C0028-2E3F-4465-876B-4CE495123F9C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -26,28 +27,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>預約式工程施工回報單</t>
   </si>
   <si>
-    <t xml:space="preserve">工程名稱：</t>
+    <t>工程名稱：</t>
   </si>
   <si>
     <t>第1次通報單</t>
   </si>
   <si>
-    <t xml:space="preserve">契約編號：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通報單編製人員：</t>
+    <t>契約編號：</t>
+  </si>
+  <si>
+    <t>通報單編製人員：</t>
   </si>
   <si>
     <t>工程地點</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>實際開工日期</t>
@@ -99,7 +100,7 @@
 5.本案1、162、233及279不得辦理追加。</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">監造單位            工務科          設計單位            總工程司室　　</t>
@@ -1187,7 +1188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1357,7 +1358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/construction_template/data/templates_blank/notification_slip.xlsx
+++ b/construction_template/data/templates_blank/notification_slip.xlsx
@@ -25,315 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>預約式工程施工回報單</t>
-  </si>
-  <si>
-    <t>工程名稱：</t>
-  </si>
-  <si>
-    <t>第1次通報單</t>
-  </si>
-  <si>
-    <t>契約編號：</t>
-  </si>
-  <si>
-    <t>通報單編製人員：</t>
-  </si>
-  <si>
-    <t>工程地點</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>實際開工日期</t>
-  </si>
-  <si>
-    <t>現場會勘日期</t>
-  </si>
-  <si>
-    <t>實際竣工日期</t>
-  </si>
-  <si>
-    <t>預定開工日期</t>
-  </si>
-  <si>
-    <t>實際使用工期</t>
-  </si>
-  <si>
-    <t>使用工期44天</t>
-  </si>
-  <si>
-    <t>預計使用工期</t>
-  </si>
-  <si>
-    <t>30日曆天</t>
-  </si>
-  <si>
-    <t>逾期天數</t>
-  </si>
-  <si>
-    <t>0日曆天</t>
-  </si>
-  <si>
-    <t>本次預估需求金額</t>
-  </si>
-  <si>
-    <t>本次實作結算金額</t>
-  </si>
-  <si>
-    <t>設計概述:</t>
-  </si>
-  <si>
-    <t>完工概述:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-2.本次通報單係111年度水利建造物檢查缺失項目修復。
-3.每項缺失改善請於回報時，均檢附有時間之施工前、中、後照片。
-4.施工期間承商應依契約勞工安全衛生等相規定辦理，並加強安全措施以維施工安全。
-5.本案1、162、233及279不得辦理追加。</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">監造單位            工務科          設計單位            總工程司室　　</t>
-  </si>
-  <si>
-    <t>竣工登錄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">預約式工程施工回報單   詳細表</t>
-  </si>
-  <si>
-    <t>項次</t>
-  </si>
-  <si>
-    <t>契約工作項目</t>
-  </si>
-  <si>
-    <t>單位</t>
-  </si>
-  <si>
-    <t>單價</t>
-  </si>
-  <si>
-    <t>本次預估需求</t>
-  </si>
-  <si>
-    <t>本次實作結算</t>
-  </si>
-  <si>
-    <t>數量</t>
-  </si>
-  <si>
-    <t>金額</t>
-  </si>
-  <si>
-    <t>壹</t>
-  </si>
-  <si>
-    <t>發包工程費</t>
-  </si>
-  <si>
-    <t>式</t>
-  </si>
-  <si>
-    <t>一</t>
-  </si>
-  <si>
-    <t>工程費</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>配合技術工之勞工</t>
-  </si>
-  <si>
-    <t>時</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>混凝土修復，蜂窩及剝落修補，水刀鑿除</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>2104.1</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>混凝土修復，鋼筋銹蝕處理，水刀鑿除</t>
-  </si>
-  <si>
-    <t>2073.6</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>混凝土修復，裂縫W＜0.3mm修補，水刀鑿除</t>
-  </si>
-  <si>
-    <t>941.74</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>混凝土修復，裂縫W＞0.3mm修補，水刀鑿除</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>1247.58</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>水泥砂漿，1:3</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>2968.16</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>伸縮縫，防洪牆(牆面伸縮縫修復(W=2cm))</t>
-  </si>
-  <si>
-    <t>455.53</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>伸縮縫，防洪牆(牆面伸縮縫修復(W=3cm))</t>
-  </si>
-  <si>
-    <t>669.04</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>產品，混凝土附屬品，伸縮縫，單液矽質填縫料</t>
-  </si>
-  <si>
-    <t>C.C.</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>清除及掘除，雜草雜木，含垃圾撿除，人工割</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>清運，雜草雜木(含垃圾)</t>
-  </si>
-  <si>
-    <t>19.31</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>油漆，一底二度(每層乾膜厚50μm以上)</t>
-  </si>
-  <si>
-    <t>129.9</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>小搬運</t>
-  </si>
-  <si>
-    <t>次</t>
-  </si>
-  <si>
-    <t>1620</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>施工輔助設施，施工架，鋼管，框式</t>
-  </si>
-  <si>
-    <t>540.44</t>
-  </si>
-  <si>
-    <t>二</t>
-  </si>
-  <si>
-    <t>材料試驗費</t>
-  </si>
-  <si>
-    <t>三</t>
-  </si>
-  <si>
-    <t>雜項工程費</t>
-  </si>
-  <si>
-    <t>四</t>
-  </si>
-  <si>
-    <t>工地環保維護費</t>
-  </si>
-  <si>
-    <t>五</t>
-  </si>
-  <si>
-    <t>安全設施及交通維持費</t>
-  </si>
-  <si>
-    <t>六</t>
-  </si>
-  <si>
-    <t>職業安全衛生費</t>
-  </si>
-  <si>
-    <t>七</t>
-  </si>
-  <si>
-    <t>自主品管費</t>
-  </si>
-  <si>
-    <t>八</t>
-  </si>
-  <si>
-    <t>稅什費(含保險費)</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1199,110 +891,178 @@
   </cols>
   <sheetData>
     <row r="1" ht="38.25" customHeight="1">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="16"/>
       <c r="B1" s="17"/>
-      <c r="C1" s="18" t="s">
-        <v>1</v>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預約式工程施工回報單</t>
+        </is>
       </c>
       <c r="D1" s="19"/>
     </row>
     <row r="2" ht="35.25" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>2</v>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程名稱：${project.name}</t>
+        </is>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
-      <c r="D2" s="51" t="s">
-        <v>3</v>
+      <c r="D2" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第${slipNo}次通報單</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>4</v>
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約編號：${project.constructionNo}</t>
+        </is>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
-      <c r="D3" s="14" t="s">
-        <v>5</v>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通報單編製人員：${compiler}</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="36.75" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="13"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程地點</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${location}</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">實際開工日期</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${actualStartDate}</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26.25" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="11"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現場會勘日期</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${surveyDate}</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">實際竣工日期</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${actualEndDate}</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26.25" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>13</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預定開工日期</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${plannedStartDate}</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">實際使用工期</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${actualDuration}</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="26.25" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>17</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預計使用工期</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${plannedDuration}</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">逾期天數</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${overdueDays}</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="26.25" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="15"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次預估需求金額</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${estimatedAmount}</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次實作結算金額</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${settlementAmount}</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>20</v>
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">設計概述:</t>
+        </is>
       </c>
       <c r="B9" s="30"/>
-      <c r="C9" s="29" t="s">
-        <v>21</v>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完工概述:</t>
+        </is>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" ht="36.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>22</v>
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${designSummary}</t>
+        </is>
       </c>
       <c r="B10" s="32"/>
-      <c r="C10" s="31" t="s">
-        <v>23</v>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${completionSummary}</t>
+        </is>
       </c>
       <c r="D10" s="32"/>
     </row>
@@ -1319,16 +1079,20 @@
       <c r="D12" s="35"/>
     </row>
     <row r="13" ht="180.75" customHeight="1">
-      <c r="A13" s="26" t="s">
-        <v>24</v>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">監造單位            工務科          設計單位            總工程司室　　</t>
+        </is>
       </c>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="s">
-        <v>25</v>
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">竣工登錄</t>
+        </is>
       </c>
       <c r="B14" s="25"/>
     </row>
@@ -1372,13 +1136,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="38.25" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="36"/>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
-      <c r="D1" s="38" t="s">
-        <v>26</v>
+      <c r="D1" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">預約式工程施工回報單   詳細表</t>
+        </is>
       </c>
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
@@ -1386,22 +1150,28 @@
       <c r="H1" s="38"/>
     </row>
     <row r="2" ht="33" customHeight="1">
-      <c r="A2" s="39" t="s">
-        <v>2</v>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程名稱：${project.name}</t>
+        </is>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
-      <c r="F2" s="50" t="s">
-        <v>3</v>
+      <c r="F2" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第${slipNo}次通報單</t>
+        </is>
       </c>
       <c r="G2" s="50"/>
       <c r="H2" s="50"/>
     </row>
     <row r="3" ht="20.1" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>4</v>
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約編號：${project.constructionNo}</t>
+        </is>
       </c>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -1412,24 +1182,36 @@
       <c r="H3" s="49"/>
     </row>
     <row r="4" ht="20.1" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>31</v>
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">項次</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約工作項目</t>
+        </is>
+      </c>
+      <c r="C4" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">單位</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">單價</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次預估需求</t>
+        </is>
       </c>
       <c r="F4" s="43"/>
-      <c r="G4" s="42" t="s">
-        <v>32</v>
+      <c r="G4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次實作結算</t>
+        </is>
       </c>
       <c r="H4" s="43"/>
     </row>
@@ -1438,358 +1220,68 @@
       <c r="B5" s="47"/>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>34</v>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">數量</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金額</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">數量</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金額</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7"/>
-      <c r="B20" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.itemNo}</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.description}</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.unit}</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.unitPrice}</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.plannedQty}</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.plannedAmount}</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.actualQty}</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">${table:items.actualAmount}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" password="9bd4"/>
